--- a/output/pdf_financials_xlsx/REG.xlsx
+++ b/output/pdf_financials_xlsx/REG.xlsx
@@ -888,31 +888,31 @@
         <v>0.086599</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.036913</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.09225700000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.038211</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.060269</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.024035</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.0106</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.6952660000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.80841</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.497301</v>
       </c>
     </row>
     <row r="13">
@@ -1585,31 +1585,31 @@
         <v>-3.458017</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.209899</v>
+        <v>-6.246812</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.492515</v>
+        <v>-3.584772</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.606802</v>
+        <v>-4.645013</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>6.869746</v>
+        <v>6.809477</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.445099</v>
+        <v>-5.469134</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.734924</v>
+        <v>-2.745524</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.068895</v>
+        <v>-3.764161</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.211692</v>
+        <v>-5.020102</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.508148</v>
+        <v>-4.005449</v>
       </c>
     </row>
     <row r="28">
@@ -1671,31 +1671,31 @@
         <v>-3.458017</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-6.209899</v>
+        <v>-6.246812</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.492515</v>
+        <v>-3.584772</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.606802</v>
+        <v>-4.645013</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.869746</v>
+        <v>6.809477</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.445099</v>
+        <v>-5.469134</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.734924</v>
+        <v>-2.745524</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.068895</v>
+        <v>-3.764161</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.211692</v>
+        <v>-5.020102</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.508148</v>
+        <v>-4.005449</v>
       </c>
     </row>
     <row r="30">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>12.640766</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>9.238633</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>7.876643</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>14.425974</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.815719</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>19.678786</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.036369</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>9.501237</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.249167</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>18.423544</v>
@@ -1975,31 +1975,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.874973</v>
+        <v>13.515739</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>9.238633</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>7.876643</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>14.425974</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.815719</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>19.678786</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.036369</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>9.501237</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.249167</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>18.423544</v>
@@ -2491,31 +2491,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>12.643343</v>
+        <v>0.002577</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>9.317339</v>
+        <v>0.078706</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>7.890972</v>
+        <v>0.014329</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14.45911</v>
+        <v>0.033136</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.863044</v>
+        <v>0.047325</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>20.239189</v>
+        <v>0.560403</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.576389</v>
+        <v>0.5400199999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9.542531</v>
+        <v>0.041294</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.664889</v>
+        <v>0.415722</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.094947</v>
@@ -5950,18 +5950,16 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.079842</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.110077</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>-0.160529</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0048</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -5995,18 +5993,16 @@
         <v>0</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.079842</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.110077</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>-0.160529</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0048</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -9462,7 +9458,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
@@ -10584,7 +10580,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -13596,7 +13592,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -22628,7 +22628,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -28798,7 +28798,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">
@@ -29466,7 +29466,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">

--- a/output/pdf_financials_xlsx/REG.xlsx
+++ b/output/pdf_financials_xlsx/REG.xlsx
@@ -3380,25 +3380,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.424057</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.317929</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.536527</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0012</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.011864</v>
       </c>
     </row>
     <row r="111">
@@ -5351,13 +5351,13 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002487</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.088258</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010512</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>-0.12847</v>
@@ -6416,13 +6416,13 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002487</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.088258</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010512</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>-0.12847</v>
@@ -6459,13 +6459,13 @@
         <v>-1.434312</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.301257</v>
+        <v>-0.303744</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.4152</v>
+        <v>-2.503458</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-3.743112</v>
+        <v>-3.753624</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-2.78376</v>
@@ -13016,7 +13016,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -15790,7 +15794,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -19234,7 +19242,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -20366,7 +20378,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
